--- a/AAII_Financials/Yearly/HOWL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HOWL_YR_FIN.xlsx
@@ -2532,7 +2532,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>29000</v>
+        <v>800</v>
       </c>
       <c r="E57" s="3">
         <v>3000</v>
@@ -2574,7 +2574,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1800</v>
+        <v>30000</v>
       </c>
       <c r="E58" s="3">
         <v>1600</v>
